--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -829,10 +829,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113330200</v>
+        <v>113330202</v>
       </c>
       <c r="B3" t="n">
-        <v>95266</v>
+        <v>95282</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563122</v>
+        <v>563129</v>
       </c>
       <c r="R3" t="n">
-        <v>6928205</v>
+        <v>6928216</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # Ved i mindre bröte</t>
+          <t>3 substratenheter # Sälglågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113330202</v>
+        <v>113330200</v>
       </c>
       <c r="B4" t="n">
-        <v>95266</v>
+        <v>95282</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563129</v>
+        <v>563122</v>
       </c>
       <c r="R4" t="n">
-        <v>6928216</v>
+        <v>6928205</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3 substratenheter # Sälglågor</t>
+          <t>2 substratenheter # Ved i mindre bröte</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -832,7 +832,7 @@
         <v>113330202</v>
       </c>
       <c r="B3" t="n">
-        <v>95282</v>
+        <v>95294</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>113330200</v>
       </c>
       <c r="B4" t="n">
-        <v>95282</v>
+        <v>95294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -829,10 +829,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113330202</v>
+        <v>113330200</v>
       </c>
       <c r="B3" t="n">
-        <v>95294</v>
+        <v>95316</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563129</v>
+        <v>563122</v>
       </c>
       <c r="R3" t="n">
-        <v>6928216</v>
+        <v>6928205</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>3 substratenheter # Sälglågor</t>
+          <t>2 substratenheter # Ved i mindre bröte</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113330200</v>
+        <v>113330202</v>
       </c>
       <c r="B4" t="n">
-        <v>95294</v>
+        <v>95316</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563122</v>
+        <v>563129</v>
       </c>
       <c r="R4" t="n">
-        <v>6928205</v>
+        <v>6928216</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2 substratenheter # Ved i mindre bröte</t>
+          <t>3 substratenheter # Sälglågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -829,10 +829,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113330200</v>
+        <v>113330202</v>
       </c>
       <c r="B3" t="n">
-        <v>95316</v>
+        <v>95320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563122</v>
+        <v>563129</v>
       </c>
       <c r="R3" t="n">
-        <v>6928205</v>
+        <v>6928216</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # Ved i mindre bröte</t>
+          <t>3 substratenheter # Sälglågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113330202</v>
+        <v>113330200</v>
       </c>
       <c r="B4" t="n">
-        <v>95316</v>
+        <v>95320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563129</v>
+        <v>563122</v>
       </c>
       <c r="R4" t="n">
-        <v>6928216</v>
+        <v>6928205</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3 substratenheter # Sälglågor</t>
+          <t>2 substratenheter # Ved i mindre bröte</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -832,7 +832,7 @@
         <v>113330202</v>
       </c>
       <c r="B3" t="n">
-        <v>95320</v>
+        <v>95326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>113330200</v>
       </c>
       <c r="B4" t="n">
-        <v>95320</v>
+        <v>95326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -829,7 +829,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113330202</v>
+        <v>113330200</v>
       </c>
       <c r="B3" t="n">
         <v>95326</v>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563129</v>
+        <v>563122</v>
       </c>
       <c r="R3" t="n">
-        <v>6928216</v>
+        <v>6928205</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>3 substratenheter # Sälglågor</t>
+          <t>2 substratenheter # Ved i mindre bröte</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,7 +944,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113330200</v>
+        <v>113330202</v>
       </c>
       <c r="B4" t="n">
         <v>95326</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563122</v>
+        <v>563129</v>
       </c>
       <c r="R4" t="n">
-        <v>6928205</v>
+        <v>6928216</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2 substratenheter # Ved i mindre bröte</t>
+          <t>3 substratenheter # Sälglågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,10 +829,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113330200</v>
+        <v>113330202</v>
       </c>
       <c r="B3" t="n">
-        <v>95326</v>
+        <v>95333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563122</v>
+        <v>563129</v>
       </c>
       <c r="R3" t="n">
-        <v>6928205</v>
+        <v>6928216</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # Ved i mindre bröte</t>
+          <t>3 substratenheter # Sälglågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113330202</v>
+        <v>113330200</v>
       </c>
       <c r="B4" t="n">
-        <v>95326</v>
+        <v>95333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563129</v>
+        <v>563122</v>
       </c>
       <c r="R4" t="n">
-        <v>6928216</v>
+        <v>6928205</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3 substratenheter # Sälglågor</t>
+          <t>2 substratenheter # Ved i mindre bröte</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,6 +1056,130 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113619420</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95322</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1455</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mikroskapania</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scapania carinthiaca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>J.B.Jack ex Lindb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Roggån, delpop2023_5 (ScUE16), Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563122</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6928205</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Mindre å nedströms kraftverksdamm. Skogen är relativt ung och mycket lövrik i denna igenväxande kulturmiljö.</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Ved i mindre bröte</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -829,10 +829,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113330202</v>
+        <v>113330200</v>
       </c>
       <c r="B3" t="n">
-        <v>95333</v>
+        <v>95338</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563129</v>
+        <v>563122</v>
       </c>
       <c r="R3" t="n">
-        <v>6928216</v>
+        <v>6928205</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>3 substratenheter # Sälglågor</t>
+          <t>2 substratenheter # Ved i mindre bröte</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113330200</v>
+        <v>113330202</v>
       </c>
       <c r="B4" t="n">
-        <v>95333</v>
+        <v>95338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563122</v>
+        <v>563129</v>
       </c>
       <c r="R4" t="n">
-        <v>6928205</v>
+        <v>6928216</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2 substratenheter # Ved i mindre bröte</t>
+          <t>3 substratenheter # Sälglågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
         <v>113619420</v>
       </c>
       <c r="B5" t="n">
-        <v>95322</v>
+        <v>95327</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>113619420</v>
       </c>
       <c r="B5" t="n">
-        <v>95327</v>
+        <v>95355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>113619420</v>
       </c>
       <c r="B5" t="n">
-        <v>95355</v>
+        <v>95359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 51756-2020 artfynd.xlsx
+++ b/artfynd/A 51756-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
